--- a/Aksiyon_Mapping.xlsx
+++ b/Aksiyon_Mapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="719">
   <si>
     <t>Ürün Barkodu</t>
   </si>
@@ -2108,9 +2108,6 @@
     <t>https://www.vatanbilgisayar.com/braun-pl5251-ipl-silk-expert-pro-5-evde-lazerle-tuy-alma-canta-venus-tiras-makinesi-2.html</t>
   </si>
   <si>
-    <t>https://cdn.vatanbilgisayar.com/Upload/PRODUCT/braun/thumb/157405-1_small.jpg</t>
-  </si>
-  <si>
     <t>https://www.vatanbilgisayar.com/braun-pl7321-ipl-skin-i-expert-evde-lazerle-tuy-alma-canta-venus-tiras-makinesi-3-basli.html</t>
   </si>
   <si>
@@ -2139,6 +2136,51 @@
   </si>
   <si>
     <t>B0D5H5M84H</t>
+  </si>
+  <si>
+    <t>https://www.mediamarkt.com.tr/tr/product/_braun-pl7211-ipl-skin-i-expert-2-baslikli-evde-lazerle-tuy-alma-canta-venus-tiras-makinesi-1253397.html</t>
+  </si>
+  <si>
+    <t>https://www.mediamarkt.com.tr/tr/product/_braun-pl5412-ipl-silkexpert-4-baslikli-evde-lazerle-tuy-alma-canta-mini-tuy-alma-makinesi-1253396.html</t>
+  </si>
+  <si>
+    <t>https://www.mediamarkt.com.tr/tr/product/_braun-pl5351-ipl-silkexpert-3-baslikli-evde-lazerle-tuy-alma-canta-venus-tiras-makinesi-1253395.html</t>
+  </si>
+  <si>
+    <t>https://www.vatanbilgisayar.com/braun-pl5412-ipl-silk-expert-pro-5-evde-lazerle-tuy-alma-canta-mini-tuy-alma-makinesi.html</t>
+  </si>
+  <si>
+    <t>https://www.hepsiburada.com/braun-ipl-skin-i-expert-evde-lazerle-tuy-alma-app-ile-canta-gillette-venus-2-baslik-pl7211-pm-HBC0000DYWP72?magaza=Hepsiburada</t>
+  </si>
+  <si>
+    <t>https://www.hepsiburada.com/braun-ipl-silk-expert-pro-5-evde-lazerle-tuy-alma-canta-gillette-venus-3-baslik-pl5351-pm-HBC0000DYWAXR?magaza=Hepsiburada</t>
+  </si>
+  <si>
+    <t>https://www.hepsiburada.com/braun-ipl-skin-i-expert-evde-lazerle-tuy-alma-app-ile-canta-gillette-venus-3-baslik-pl7321-pm-HBC0000DYW99P?magaza=Hepsiburada</t>
+  </si>
+  <si>
+    <t>B0GTWNZQXW</t>
+  </si>
+  <si>
+    <t>B0CV11F44H</t>
+  </si>
+  <si>
+    <t>https://www.hepsiburada.com/braun-brhd155e-hd1-55-difuzorlu-sac-kurutma-makinesi-2-baslikli-1800w-pm-HBC0000AXMDLG?magaza=Hepsiburada</t>
+  </si>
+  <si>
+    <t>https://www.teknosa.com/braun-silk-expert-pro-5-pl5351-ipl-lazer-epilasyon-cihazi-p-100000062435?shopId=teknosa</t>
+  </si>
+  <si>
+    <t>https://www.teknosa.com/braun-silk-expert-pro-5-pl5251-ipl-lazer-epilasyon-cihazi-p-100000062436?shopId=teknosa</t>
+  </si>
+  <si>
+    <t>https://www.teknosa.com/braun-silk-expert-pro-pl5412-ipl-lazer-epilasyon-cihazi-p-100000062450?shopId=teknosa</t>
+  </si>
+  <si>
+    <t>https://www.teknosa.com/braun-skin-i-expert-pl7321-ipl-lazer-epilasyon-cihazi-p-100000062460?shopId=teknosa</t>
+  </si>
+  <si>
+    <t>https://www.hepsiburada.com/braun-ipl-skin-i-expert-evde-lazerle-tuy-alma-app-ile-canta-gillette-venus-4-baslik-pl7431-p-HBCV0000DYW99I?magaza=Hepsiburada&amp;utm_source=akakce&amp;utm_medium=cpc&amp;utm_campaign=sc%3Ahb-ecom.sr%3Aakakce.md%3Apricecomp&amp;utm_content=agnm%3Ahb&amp;wt_pc=akakce&amp;adj_t=1fmpah5v_1fmqteof&amp;adj_campaign=akakce&amp;v=1.47.2</t>
   </si>
 </sst>
 </file>
@@ -2965,7 +3007,7 @@
       <c r="E2" s="33"/>
       <c r="F2" s="23"/>
       <c r="G2" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H2" s="23" t="s">
         <v>689</v>
@@ -2992,9 +3034,11 @@
       <c r="E3" s="33">
         <v>1130959133</v>
       </c>
-      <c r="F3" s="23"/>
+      <c r="F3" s="23" t="s">
+        <v>718</v>
+      </c>
       <c r="G3" s="6" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H3" s="23"/>
       <c r="I3" s="23"/>
@@ -3019,14 +3063,18 @@
       <c r="E4" s="33">
         <v>1130962186</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="23" t="s">
+        <v>710</v>
+      </c>
       <c r="G4" s="6" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
+      <c r="I4" s="23" t="s">
+        <v>717</v>
+      </c>
       <c r="J4" s="23" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>4</v>
@@ -3048,7 +3096,7 @@
       <c r="E5" s="33"/>
       <c r="F5" s="23"/>
       <c r="G5" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H5" s="23"/>
       <c r="I5" s="23"/>
@@ -3108,9 +3156,15 @@
       <c r="E7" s="33">
         <v>1130965240</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="23"/>
+      <c r="F7" s="23" t="s">
+        <v>708</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>704</v>
+      </c>
       <c r="I7" s="23"/>
       <c r="J7" s="23"/>
       <c r="K7" s="3" t="s">
@@ -3168,12 +3222,16 @@
       <c r="E9" s="33"/>
       <c r="F9" s="23"/>
       <c r="G9" s="6" t="s">
-        <v>702</v>
-      </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
+        <v>701</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>705</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>716</v>
+      </c>
       <c r="J9" s="23" t="s">
-        <v>694</v>
+        <v>707</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>4</v>
@@ -3224,12 +3282,18 @@
       <c r="E11" s="33">
         <v>1130969069</v>
       </c>
-      <c r="F11" s="23"/>
+      <c r="F11" s="23" t="s">
+        <v>709</v>
+      </c>
       <c r="G11" s="6" t="s">
-        <v>698</v>
-      </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
+        <v>697</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>706</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>714</v>
+      </c>
       <c r="J11" s="23" t="s">
         <v>692</v>
       </c>
@@ -3253,7 +3317,7 @@
       <c r="E12" s="33"/>
       <c r="F12" s="23"/>
       <c r="G12" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
@@ -3280,12 +3344,14 @@
       </c>
       <c r="F13" s="23"/>
       <c r="G13" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H13" s="23" t="s">
         <v>690</v>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="23" t="s">
+        <v>715</v>
+      </c>
       <c r="J13" s="23" t="s">
         <v>693</v>
       </c>
@@ -3336,7 +3402,7 @@
       <c r="E15" s="33"/>
       <c r="F15" s="23"/>
       <c r="G15" s="6" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H15" s="23"/>
       <c r="I15" s="23"/>
@@ -3484,7 +3550,9 @@
       </c>
       <c r="E20" s="33"/>
       <c r="F20" s="23"/>
-      <c r="G20" s="6"/>
+      <c r="G20" s="6" t="s">
+        <v>712</v>
+      </c>
       <c r="H20" s="23"/>
       <c r="I20" s="23"/>
       <c r="J20" s="23"/>
@@ -6034,7 +6102,9 @@
         <v>169</v>
       </c>
       <c r="E102" s="33"/>
-      <c r="F102" s="23"/>
+      <c r="F102" s="23" t="s">
+        <v>713</v>
+      </c>
       <c r="G102" s="6" t="s">
         <v>479</v>
       </c>

--- a/Aksiyon_Mapping.xlsx
+++ b/Aksiyon_Mapping.xlsx
@@ -2180,7 +2180,7 @@
     <t>https://www.teknosa.com/braun-skin-i-expert-pl7321-ipl-lazer-epilasyon-cihazi-p-100000062460?shopId=teknosa</t>
   </si>
   <si>
-    <t>https://www.hepsiburada.com/braun-ipl-skin-i-expert-evde-lazerle-tuy-alma-app-ile-canta-gillette-venus-4-baslik-pl7431-p-HBCV0000DYW99I?magaza=Hepsiburada&amp;utm_source=akakce&amp;utm_medium=cpc&amp;utm_campaign=sc%3Ahb-ecom.sr%3Aakakce.md%3Apricecomp&amp;utm_content=agnm%3Ahb&amp;wt_pc=akakce&amp;adj_t=1fmpah5v_1fmqteof&amp;adj_campaign=akakce&amp;v=1.47.2</t>
+    <t>https://www.hepsiburada.com/braun-ipl-skin-i-expert-evde-lazerle-tuy-alma-app-ile-canta-gillette-venus-4-baslik-pl7431-pm-HBC0000DYW99H?magaza=Hepsiburada</t>
   </si>
 </sst>
 </file>

--- a/Aksiyon_Mapping.xlsx
+++ b/Aksiyon_Mapping.xlsx
@@ -5954,8 +5954,12 @@
       </c>
     </row>
     <row r="97" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
+      <c r="A97" s="6">
+        <v>1501001171</v>
+      </c>
+      <c r="B97" s="6">
+        <v>1298</v>
+      </c>
       <c r="C97" s="6">
         <v>3030050197549</v>
       </c>
@@ -6234,8 +6238,12 @@
       </c>
     </row>
     <row r="107" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
+      <c r="A107" s="6">
+        <v>1501080561</v>
+      </c>
+      <c r="B107" s="6">
+        <v>1299</v>
+      </c>
       <c r="C107" s="6">
         <v>3030050197631</v>
       </c>
@@ -9103,8 +9111,10 @@
     <hyperlink ref="D12" r:id="rId298"/>
     <hyperlink ref="D13" r:id="rId299"/>
     <hyperlink ref="D15" r:id="rId300"/>
+    <hyperlink ref="D97" r:id="rId301"/>
+    <hyperlink ref="D107" r:id="rId302"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId301"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId303"/>
 </worksheet>
 </file>